--- a/output/xlsx/server-spec-20260526.xlsx
+++ b/output/xlsx/server-spec-20260526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NT130\Desktop\인턴\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48FF2FB3-EBB0-4F6F-A2B3-69597BE278FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6BD267-270F-4B9E-A9CA-EF112433DC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,12 +52,6 @@
     <t>Disk</t>
   </si>
   <si>
-    <t>192.168.100.125</t>
-  </si>
-  <si>
-    <t>apps2-sever</t>
-  </si>
-  <si>
     <t>Ubuntu 20.04.6 LTS</t>
   </si>
   <si>
@@ -73,12 +67,20 @@
     <t>31Gi</t>
   </si>
   <si>
-    <t>예시</t>
+    <t>sda     disk   3.7T    1 TOSHIBA_HDWQ140
+nvme0n1 disk 465.8G    0 Samsung SSD 970 EVO Plus 500GB</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>sda     disk   3.7T    1 TOSHIBA_HDWQ140
-nvme0n1 disk 465.8G    0 Samsung SSD 970 EVO Plus 500GB</t>
+    <t>example-server-01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>example-hostname</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10.0.0.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -505,31 +507,31 @@
     </row>
     <row r="2" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.45">
